--- a/daily_matches/job_matches_2026-09-23.xlsx
+++ b/daily_matches/job_matches_2026-09-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>Bain Capital</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,77 +486,77 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Copilot, Pinecone, Cortex, MLflow</t>
+          <t>AI Engineer, Data Scientist, RAG, Pinecone, Prompt Engineering, XGBoost, S3, EC2, MLflow, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83876c66e135b993</t>
+          <t>https://www.indeed.com/viewjob?jk=eca7f94335380452</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>Alignment Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Copilot, Pinecone, Cortex, MLflow</t>
+          <t>Generative AI, LangChain, Redshift, BigQuery, Data Lake, MLflow, Git, Snowflake, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4924b3389452957</t>
+          <t>https://www.indeed.com/viewjob?jk=1611fa9de2f7504b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior AI Ops / DevOps Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Blue Cross and Blue Shield of Minnesota</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, MLflow, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RAG, Copilot, S3, Glue, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=040c156b15abd039</t>
+          <t>https://www.indeed.com/viewjob?jk=31bf226ac97de61e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer, Client Solutions Group</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>Willdan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Anaheim, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Pinecone, Cortex, S3, MLflow, Docker, CI/CD</t>
+          <t>Generative AI, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cba42b7feabaab8</t>
+          <t>https://www.indeed.com/viewjob?jk=8d1298ac76effc74</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Analyst - ERP &amp; Master Data</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TransTech Group</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Synapse, Dataflow, Git, Databricks, PySpark, Power BI, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49c2343d736f4c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=70278c6707b92e9e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Data Engineer II</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Kafka, Cassandra, NoSQL, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9b4607cbdf4a3d4</t>
+          <t>https://www.indeed.com/viewjob?jk=a25e08cbc61c8f9c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Cloud / AWS Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Reflex Media Inc</t>
+          <t>Pika</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, Kubernetes, CI/CD, Terraform, Redshift, PostgreSQL, MySQL, Python</t>
+          <t>RAG, Redshift, BigQuery, Kinesis, Docker, Kubernetes, Snowflake, BigQuery, Redshift, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=901aac12afba9b93</t>
+          <t>https://www.indeed.com/viewjob?jk=126cb889e15ed9cd</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI Native Development</t>
+          <t>Consultant, AI Risk &amp; Validation</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Kinesis, CI/CD, Terraform, Kafka, PostgreSQL, Python, SQL</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea9ef8693c4fa599</t>
+          <t>https://www.indeed.com/viewjob?jk=1de657799a6cb138</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Engineer I</t>
+          <t>Consultant, AI Risk &amp; Validation</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Dataflow, CI/CD, Git, BigQuery, Kafka, Python, SQL, R</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ca08863d5287990</t>
+          <t>https://www.indeed.com/viewjob?jk=3535248a590d2346</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Consultant, AI Risk &amp; Validation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, Docker, Kubernetes, Jenkins, Terraform, Git, NoSQL, SQL, R, Java</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77c13363e54e5087</t>
+          <t>https://www.indeed.com/viewjob?jk=10a5f6eb26a11843</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Development Engineer, Cloud</t>
+          <t>Consultant, AI Risk &amp; Validation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sonos</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, EC2, Kubernetes, Git, NoSQL, SQL, R</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7afeb40ffabb89e1</t>
+          <t>https://www.indeed.com/viewjob?jk=996ab6b5455b4192</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C# Full Stack Developer</t>
+          <t>Consultant, AI Risk &amp; Validation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Globant</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d96c65fe6b68f304</t>
+          <t>https://www.indeed.com/viewjob?jk=d6e30e2ca83a1353</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer II - AWS/PySpark/ETL</t>
+          <t>Consultant, AI Risk &amp; Validation</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, Git, Snowflake, Databricks, PySpark, Python, SQL, R</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa1cc23a36ed4493</t>
+          <t>https://www.indeed.com/viewjob?jk=894e7f6f24619d33</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Analytics Engineer Sr - Remote</t>
+          <t>Consultant, AI Risk &amp; Validation</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Prime Therapeutics</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Kubernetes, Git, BigQuery, Python, SQL, R, Scala</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d51b210f461aeade</t>
+          <t>https://www.indeed.com/viewjob?jk=3f5aef5eb6e84ed2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Consultant, AI Risk &amp; Validation</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dropbox</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Kinesis, Databricks, Kafka, Python, SQL, R, Java</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e37e262d8bc84b</t>
+          <t>https://www.indeed.com/viewjob?jk=8df8d52b78f6e091</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Associate Solutions Designer, Automation</t>
+          <t>Consultant, AI Risk &amp; Validation</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, Jenkins, Git, Python, R, Java</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9352577094e32eae</t>
+          <t>https://www.indeed.com/viewjob?jk=35df91344c56afed</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Consultant, AI Risk &amp; Validation</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>WorkOS</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Git, Snowflake, Python, SQL, R</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c58ad8f77c200b</t>
+          <t>https://www.indeed.com/viewjob?jk=74fcd0a12572de66</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Engineer, Performance Management</t>
+          <t>Consultant, AI Risk &amp; Validation</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Lake, FastAPI, CI/CD, Git, Snowflake, Power BI, Python, SQL, R, Scala</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e0346f80c455f7d</t>
+          <t>https://www.indeed.com/viewjob?jk=2756ba3e16e700da</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Consultant, AI Risk &amp; Validation</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Warrenville, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Copilot, Docker, Kubernetes, CI/CD, R, Java, Scala</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59133388be98940a</t>
+          <t>https://www.indeed.com/viewjob?jk=658fc16536f1ea3e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr AI Engineer I</t>
+          <t>Consultant, AI Risk &amp; Validation</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0f66b1a3ebd9a53</t>
+          <t>https://www.indeed.com/viewjob?jk=77284adbc68f580b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Java Software Engineer III</t>
+          <t>Consultant, AI Risk &amp; Validation</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Terraform, Kafka, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dca990acc894d8c</t>
+          <t>https://www.indeed.com/viewjob?jk=b22232275525ce9c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Junior QA Automation Engineer / SDET</t>
+          <t>Consultant, AI Risk &amp; Validation</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Jenkins, GitHub Actions, Git, SQL, R, Java, Scala</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=363b3250fe4364f8</t>
+          <t>https://www.indeed.com/viewjob?jk=ca2e23c8e447d4a9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Consultant, AI Risk &amp; Validation</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Syngenta</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Generative AI, Data Lake, Git, Snowflake, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3565a8fb2153fa3a</t>
+          <t>https://www.indeed.com/viewjob?jk=54bcbdb779bbe682</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Consultant, AI Risk &amp; Validation</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Skyworks Solutions</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Databricks, R, Scala, Optimization, Hypothesis Testing</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67a222626b97796e</t>
+          <t>https://www.indeed.com/viewjob?jk=54cc37c018a4b653</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Junior QA Automation Engineer / SDET</t>
+          <t>Consultant, AI Risk &amp; Validation</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Jenkins, GitHub Actions, Git, SQL, R, Java, Scala</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16752aee7713b378</t>
+          <t>https://www.indeed.com/viewjob?jk=bf1f4ceaa2ec3f8f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Consultant, Data &amp; Analytics, NA</t>
+          <t>Consultant, AI Risk &amp; Validation</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Git, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df7e6baa7a7dd0a0</t>
+          <t>https://www.indeed.com/viewjob?jk=97d3879d42fea0bd</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer II (Angular, Java)</t>
+          <t>Consultant, AI Risk &amp; Validation</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, SQL, R, Java</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3400099003f5cba2</t>
+          <t>https://www.indeed.com/viewjob?jk=641a1f2abd018427</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer II (Angular, Java)</t>
+          <t>Consultant, AI Risk &amp; Validation</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, SQL, R, Java</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69a4d1b0a1c615f0</t>
+          <t>https://www.indeed.com/viewjob?jk=82c47ff507bb6683</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer II (Angular, Java)</t>
+          <t>Consultant, AI Risk &amp; Validation</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, SQL, R, Java</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa71cf7fad2b8f2c</t>
+          <t>https://www.indeed.com/viewjob?jk=a64fc88fc6576fb1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>Consultant, AI Risk &amp; Validation</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, GitHub Actions, Terraform, Git, Databricks, Python, SQL, R, Java, Scala</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,67 +1511,67 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d727a12d260ca4e6</t>
+          <t>https://www.indeed.com/viewjob?jk=8b942492aba84e7a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Consultant, AI Risk &amp; Validation</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, CI/CD, Snowflake, Databricks, PySpark, Python, SQL, R, Scala</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c290ef08047b759</t>
+          <t>https://www.indeed.com/viewjob?jk=05d2ba64d6be965d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Product Security Engineer, AI ML</t>
+          <t>Consultant, AI Risk &amp; Validation</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Norstella</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, LLaMA, Gemini, Pinecone, Prompt Engineering, CI/CD, Git, Python, R, Scala</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6688b98722d69570</t>
+          <t>https://www.indeed.com/viewjob?jk=eb95394932928c4e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Platform)</t>
+          <t>Consultant, AI Risk &amp; Validation</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MIA Labs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>BigQuery, FastAPI, CI/CD, Git, Snowflake, BigQuery, Python, SQL, R, Scala</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1a60bd31f33e718</t>
+          <t>https://www.indeed.com/viewjob?jk=32628eb89c6bca45</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Associate Developer, Research Technology</t>
+          <t>Software engineer, generative AI</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Writer</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Databricks, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Pinecone, FastAPI, Docker, Kubernetes, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,19 +1651,19 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4b777817204a676</t>
+          <t>https://www.indeed.com/viewjob?jk=65ecbae3eac23242</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Software engineer, generative AI</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Writer</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1672,11 +1672,11 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Jenkins, Git, Kafka, R, Java</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Pinecone, FastAPI, Docker, Kubernetes, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f2cd8293a16a865</t>
+          <t>https://www.indeed.com/viewjob?jk=37428f7c2978157f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Software engineer, generative AI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Thrive Therapies</t>
+          <t>Writer</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RAG, S3, FastAPI, Terraform, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Pinecone, FastAPI, Docker, Kubernetes, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,102 +1721,102 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfc788826255acf</t>
+          <t>https://www.indeed.com/viewjob?jk=541a32d29029095c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Specialist - Software Engineering</t>
+          <t>Senior Software Engineer - ai automation medical billing platform</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Relentless Talent</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, Kafka, MongoDB, SQL, R, Java</t>
+          <t>RAG, Docker, GitHub Actions, Git, Snowflake, PostgreSQL, MySQL, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=549a9d62bda35e2b</t>
+          <t>https://www.indeed.com/viewjob?jk=69d642c554413fbe</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Software Engineer - ai automation medical billing platform</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Relentless Talent</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Jenkins, Git, Kafka, R, Java</t>
+          <t>RAG, Docker, GitHub Actions, Git, Snowflake, PostgreSQL, MySQL, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101251186a0a242a</t>
+          <t>https://www.indeed.com/viewjob?jk=818c7178aa0280e0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Engineer, Machine Learning, Vision</t>
+          <t>Back-end Engineer - Data Platforms</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Rockwell Automation</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Git, Python, R, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Snowflake, Databricks, PySpark, Kafka, Hadoop, Python</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa57213a7b61ef89</t>
+          <t>https://www.indeed.com/viewjob?jk=ebb387f8fd246816</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Technical Engineer (Production Liability Engineer)</t>
+          <t>Applied AI Site Reliability Engineer II - PxE A&amp;A</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>M&amp;T Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, AKS, CI/CD, Python, SQL, R, Scala</t>
+          <t>RAG, MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bef57255c79d57a0</t>
+          <t>https://www.indeed.com/viewjob?jk=293a95bba31efbab</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior AI Architect</t>
+          <t>Applied AI Site Reliability Engineer II - PxE A&amp;A</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, MLflow, Kubernetes, CI/CD, Terraform, Git, R, Scala</t>
+          <t>RAG, MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9775b87662f6b188</t>
+          <t>https://www.indeed.com/viewjob?jk=90798cf9ad992e58</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>R&amp;D PhD Summer Intern - AI Research Engineer</t>
+          <t>Applied AI Site Reliability Engineer II - PxE A&amp;A</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>LangChain, RAG, TensorFlow, PyTorch, FastAPI, Docker, Python, R, Scala</t>
+          <t>RAG, MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa8d4675fd801c8</t>
+          <t>https://www.indeed.com/viewjob?jk=76a0c64002bbb5c1</t>
         </is>
       </c>
     </row>
@@ -1943,100 +1943,2480 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Community Choice Credit Union</t>
+          <t>Function Health</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jackson, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>CI/CD, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, BigQuery, Terraform, Git, Snowflake, Databricks, BigQuery, Kafka, Python</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad209d8bad2edfe</t>
+          <t>https://www.indeed.com/viewjob?jk=8d332f2047edfa45</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Senior Data Analyst - Dow Jones Energy Product Management</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tyndale Company</t>
+          <t>News Corp</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pipersville, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
+          <t>RAG, Athena, BigQuery, Git, Snowflake, BigQuery, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e8ce5c4d4815bf9</t>
+          <t>https://www.indeed.com/viewjob?jk=857537ffca72eab2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Architect, Corporate Services</t>
+          <t>Senior Data Platfrom Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Data Lake, CI/CD, Git, Databricks, PySpark, Power BI, MicroStrategy, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc974eac3e508ce6</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Data Lake, CI/CD, Git, Databricks, PySpark, Power BI, MicroStrategy, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e85b5d56e27bdfb8</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Sr. iOS Developer--Hybrid</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Bridgewater, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, Jenkins, Git, PostgreSQL, MySQL, Cassandra, SQL, R</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2f579d7993e4d2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c343a7d6432ffeaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e60054b9631d7895</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99aade9079199e44</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb5a4840f3df3c6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55abd889581cdc48</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e3febde783536e21</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1be19f91eec7a842</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7698c96689f48a9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d2e1386f9d607f38</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f2ca862816ed069</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a40909cafc968d82</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=124344ebd08b7526</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0ef6c1eb38b0db9</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b780dcc242beb567</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a03180188c81f9bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a037168850b8fe0</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45cd4b8d959d97ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52080037fabe4cb1</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=69224b4d176dd4a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ce9dba6d19c8b82</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7c5344293aa5ed77</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fea3b3cc46faeb2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3672ad48951be20</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c45dff0f36a9a356</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e91b7a712b7a165</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3d69f9412407b80</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d48fbbfaa3d0a97</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c300f1e448116fd7</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=316adbd72ad7e2e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f219232c6b6eef2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0bb31aa937d723cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=884c614c785d6835</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ecedaabbce0a0b5b</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eea12c90a4a047af</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=28b6e9e7e6b5c6aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c0e09d9843111bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b10af7d10426fa4</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Full Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Kirby Building Systems</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Portland, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba021890de8dea89</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Sr Forward Deployed Engineer (Palantir Foundry &amp; Custom Development)</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Data Scientist, CI/CD, Git, Snowflake, Databricks, PostgreSQL, MongoDB, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34498abb3a8be8a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>WellSky</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Overland Park, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, CI/CD, Git, BigQuery, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d0888bf081a07cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Sally Beauty</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Denton, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>RAG, S3, Data Lake, Databricks, PySpark, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0864fe655aae7888</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Versant Health</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Troy, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Synapse, Data Lake, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07b683fa1519b020</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Versant Health</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Synapse, Data Lake, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7a1725a49cda6dda</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Senior Consultant, AI Services</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>InvestorFlow</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, Git, Snowflake, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fba78e9af19a43b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Distributed Systems Engineer, Vehicle Fulfillment</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Fremont, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, R, Scala</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a0fe96c02c778b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior Engineer -Creative Marketing</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Catalyst Brands</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Git, Kafka, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1a6e5202bbaaf18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Sr Product Security Engineer, AI &amp; DevSecOps</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>McKesson</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b8ba8f92a1292eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Business Intelligence Engineer II: Partner Analytics - Hybrid</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Rocket</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Snowflake, Tableau, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=637673cd1f7765b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Java Full Stack Developer-Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Kafka, MongoDB, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb0ee02388fd9a1d</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>SC Engineers</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Beltsville, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, Power BI, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2661c4a3a6b07f81</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Intentsify</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>S3, Docker, Kubernetes, AKS, CI/CD, Terraform, Snowflake, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d89a533339b416c</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Software Engineer, ML Infrastructure, Level 5</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
         <v>10</v>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Terraform, Snowflake, Databricks, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c3007521d1e10c7</t>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4cad11433588f70d</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Sr Technical Analyst/Prog Ent App</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Avangrid</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Orange, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Generative AI, Copilot, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ea1b275b8152311</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Git, Snowflake, PostgreSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c33cfcad7d1aa65e</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Data Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Hubble Network</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, Kinesis, Redshift, Kafka, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a000c1d1d33d8b12</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>AI engineer</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Writer</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8cc20f9386f214c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>AI engineer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Writer</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3eb3f306bda536fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>AI Engineer I</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Universal Leaf Tobacco Company, Inc.</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Docker, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b8468e3514144cdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Data Science Intern - Summer 2027</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Rippling</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, AKS, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f2c869f55f6a0f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Community Choice Credit Union</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Warren, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>CI/CD, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21899fbf482a9cd2</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Community Choice Credit Union</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Jackson, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>CI/CD, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9457f2c72938dbd5</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Community Choice Credit Union</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Holland, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>CI/CD, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f79614628dc966f</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Community Choice Credit Union</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Farmington Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>CI/CD, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc4be70d8a478d8a</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Software engineer, agents</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Writer</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5700052fa2fc6f53</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Software engineer, agents</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Writer</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a8c6573ec630ba5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Software engineer, agents</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Writer</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cec61be25df497ab</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-23.xlsx
+++ b/daily_matches/job_matches_2026-09-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bain Capital</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Pinecone, Prompt Engineering, XGBoost, S3, EC2, MLflow, Docker</t>
+          <t>Data Scientist, LangChain, RAG, TensorFlow, BigQuery, Data Lake, Dataflow, Kubernetes, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca7f94335380452</t>
+          <t>https://www.indeed.com/viewjob?jk=8dd495afc5140159</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Alignment Health</t>
+          <t>Team TTI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, Redshift, BigQuery, Data Lake, MLflow, Git, Snowflake, Databricks, BigQuery</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Keras, MLflow, CI/CD, Databricks, Matplotlib</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1611fa9de2f7504b</t>
+          <t>https://www.indeed.com/viewjob?jk=d6df5f550c6a3e5b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Blue Cross and Blue Shield of Minnesota</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Glue, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks</t>
+          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31bf226ac97de61e</t>
+          <t>https://www.indeed.com/viewjob?jk=d80c6adab1193eaf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Engineer 5</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Willdan</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Anaheim, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d1298ac76effc74</t>
+          <t>https://www.indeed.com/viewjob?jk=3a1e95e5123a2b15</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>Data Engineer 5 - Enterprise Risk Management</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL, Python</t>
+          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70278c6707b92e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=a45f08af4f7be5f6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>Data Engineer 4 - Nexus Products</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL, Python</t>
+          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a25e08cbc61c8f9c</t>
+          <t>https://www.indeed.com/viewjob?jk=36fc31dc37d05722</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pika</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Kinesis, Docker, Kubernetes, Snowflake, BigQuery, Redshift, Kafka</t>
+          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=126cb889e15ed9cd</t>
+          <t>https://www.indeed.com/viewjob?jk=45e14228c1ed2aed</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Consultant, AI Risk &amp; Validation</t>
+          <t>Data Engineer 4 - Payment Networks</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
+          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1de657799a6cb138</t>
+          <t>https://www.indeed.com/viewjob?jk=f8d0c3f139798fd9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Consultant, AI Risk &amp; Validation</t>
+          <t>Data Engineer 4 - HR Tech</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
+          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3535248a590d2346</t>
+          <t>https://www.indeed.com/viewjob?jk=010f3637940ea854</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Consultant, AI Risk &amp; Validation</t>
+          <t>Data Engineer 5 (SEO/GEO, AdTech )</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
+          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10a5f6eb26a11843</t>
+          <t>https://www.indeed.com/viewjob?jk=e9a8f6941c1a4549</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Consultant, AI Risk &amp; Validation</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
+          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=996ab6b5455b4192</t>
+          <t>https://www.indeed.com/viewjob?jk=0db4720c664a5a3f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Consultant, AI Risk &amp; Validation</t>
+          <t>Data Engineer 5 (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
+          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6e30e2ca83a1353</t>
+          <t>https://www.indeed.com/viewjob?jk=220dab7fe793042b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Consultant, AI Risk &amp; Validation</t>
+          <t>Machine Learning Engineer II - Operations</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Keras, MLflow, CI/CD, Databricks, Matplotlib</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=894e7f6f24619d33</t>
+          <t>https://www.indeed.com/viewjob?jk=d1f1b289a3e5556a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Consultant, AI Risk &amp; Validation</t>
+          <t>Full-stack Engineer 5 (Go, TypeScript and Angular)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f5aef5eb6e84ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=81ff3ef325447a98</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Consultant, AI Risk &amp; Validation</t>
+          <t>Full-stack Engineer 5 (Nodejs/Go/Angularjs)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8df8d52b78f6e091</t>
+          <t>https://www.indeed.com/viewjob?jk=9813442a220867be</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Consultant, AI Risk &amp; Validation</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35df91344c56afed</t>
+          <t>https://www.indeed.com/viewjob?jk=70843ae9e366dd5b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Consultant, AI Risk &amp; Validation</t>
+          <t>Full - Stack Engineer 5 (Remote - Eligible)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fcd0a12572de66</t>
+          <t>https://www.indeed.com/viewjob?jk=877ad6c20024fb1a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Consultant, AI Risk &amp; Validation</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2756ba3e16e700da</t>
+          <t>https://www.indeed.com/viewjob?jk=6979868bb95d63f0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Consultant, AI Risk &amp; Validation</t>
+          <t>Full-stack Engineer 4 - RiskTech</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=658fc16536f1ea3e</t>
+          <t>https://www.indeed.com/viewjob?jk=f2960b2498873f28</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Consultant, AI Risk &amp; Validation</t>
+          <t>Full Stack Engineer 5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77284adbc68f580b</t>
+          <t>https://www.indeed.com/viewjob?jk=b743b91aec079a75</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Consultant, AI Risk &amp; Validation</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b22232275525ce9c</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb66ff5f4ef065f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Consultant, AI Risk &amp; Validation</t>
+          <t>Full-stack Engineer 4 (Python, Java)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca2e23c8e447d4a9</t>
+          <t>https://www.indeed.com/viewjob?jk=c9046de91e154d69</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Consultant, AI Risk &amp; Validation</t>
+          <t>Full-stack Engineer 5 ( Python, AWS)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54bcbdb779bbe682</t>
+          <t>https://www.indeed.com/viewjob?jk=5e4de127a7227d81</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Consultant, AI Risk &amp; Validation</t>
+          <t>Full-stack Engineer 5 (Golang, Java, AWS)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54cc37c018a4b653</t>
+          <t>https://www.indeed.com/viewjob?jk=f3a9ee8f682a9c78</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Consultant, AI Risk &amp; Validation</t>
+          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf1f4ceaa2ec3f8f</t>
+          <t>https://www.indeed.com/viewjob?jk=6faf5ca1640fcd31</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Consultant, AI Risk &amp; Validation</t>
+          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97d3879d42fea0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=42133a298638cb9b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Consultant, AI Risk &amp; Validation</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=641a1f2abd018427</t>
+          <t>https://www.indeed.com/viewjob?jk=a708182f9a1da64d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Consultant, AI Risk &amp; Validation</t>
+          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82c47ff507bb6683</t>
+          <t>https://www.indeed.com/viewjob?jk=76c8a5b4fcc58505</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Consultant, AI Risk &amp; Validation</t>
+          <t>Full-stack Engineer 5 - Shopping (Remote-Eligible)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a64fc88fc6576fb1</t>
+          <t>https://www.indeed.com/viewjob?jk=419688dc0cbfaf98</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Consultant, AI Risk &amp; Validation</t>
+          <t>Full-stack Engineer 5 (Java, Scala, AWS)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b942492aba84e7a</t>
+          <t>https://www.indeed.com/viewjob?jk=c997daa05db4e0c7</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Consultant, AI Risk &amp; Validation</t>
+          <t>Full Stack Engineer 4 (Go, AWS)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05d2ba64d6be965d</t>
+          <t>https://www.indeed.com/viewjob?jk=6a9874c783fb4a03</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Consultant, AI Risk &amp; Validation</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb95394932928c4e</t>
+          <t>https://www.indeed.com/viewjob?jk=1f96da918db85a2a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Consultant, AI Risk &amp; Validation</t>
+          <t>Full-stack Engineer 4 (Java, Scala, AWS)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32628eb89c6bca45</t>
+          <t>https://www.indeed.com/viewjob?jk=b9e0187cbe4c2e40</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software engineer, generative AI</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Writer</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Pinecone, FastAPI, Docker, Kubernetes, Git, PostgreSQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65ecbae3eac23242</t>
+          <t>https://www.indeed.com/viewjob?jk=900df92ddc778d5f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software engineer, generative AI</t>
+          <t>Full-stack Engineer 4 (JavaScript, React)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Writer</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Pinecone, FastAPI, Docker, Kubernetes, Git, PostgreSQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37428f7c2978157f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7c346fa6453ffb9</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software engineer, generative AI</t>
+          <t>Full-stack Engineer 5 (Go/Java, Angular, AWS)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Writer</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Pinecone, FastAPI, Docker, Kubernetes, Git, PostgreSQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,102 +1721,102 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=541a32d29029095c</t>
+          <t>https://www.indeed.com/viewjob?jk=c039bc465260bc95</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ai automation medical billing platform</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Relentless Talent</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RAG, Docker, GitHub Actions, Git, Snowflake, PostgreSQL, MySQL, MongoDB, NoSQL, Python</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69d642c554413fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=54e236865193f8a0</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ai automation medical billing platform</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Relentless Talent</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RAG, Docker, GitHub Actions, Git, Snowflake, PostgreSQL, MySQL, MongoDB, NoSQL, Python</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=818c7178aa0280e0</t>
+          <t>https://www.indeed.com/viewjob?jk=b667ebd325202576</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Back-end Engineer - Data Platforms</t>
+          <t>Full-stack Engineer 5 (Golang, AWS)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Snowflake, Databricks, PySpark, Kafka, Hadoop, Python</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebb387f8fd246816</t>
+          <t>https://www.indeed.com/viewjob?jk=672e371e8fd60859</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Applied AI Site Reliability Engineer II - PxE A&amp;A</t>
+          <t>Full-stack Engineer 4 (React, TypeScript, AWS)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RAG, MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python, SQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=293a95bba31efbab</t>
+          <t>https://www.indeed.com/viewjob?jk=346a7f081a67b46c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Applied AI Site Reliability Engineer II - PxE A&amp;A</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RAG, MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python, SQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90798cf9ad992e58</t>
+          <t>https://www.indeed.com/viewjob?jk=7b21934bf2433e6a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Applied AI Site Reliability Engineer II - PxE A&amp;A</t>
+          <t>Full-stack Engineer 4 (Scala, React, AWS)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RAG, MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python, SQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76a0c64002bbb5c1</t>
+          <t>https://www.indeed.com/viewjob?jk=2af3b2e528eb8c47</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-stack Engineer 4 (Scala, React, AWS)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Function Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Terraform, Git, Snowflake, Databricks, BigQuery, Kafka, Python</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d332f2047edfa45</t>
+          <t>https://www.indeed.com/viewjob?jk=51fd20841ca9c754</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Analyst - Dow Jones Energy Product Management</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>News Corp</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RAG, Athena, BigQuery, Git, Snowflake, BigQuery, Tableau, Power BI, Python, SQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=857537ffca72eab2</t>
+          <t>https://www.indeed.com/viewjob?jk=619531dae358928f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Platfrom Engineer</t>
+          <t>Full-stack Engineer 4 (Python, AWS)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Data Lake, CI/CD, Git, Databricks, PySpark, Power BI, MicroStrategy, Python, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc974eac3e508ce6</t>
+          <t>https://www.indeed.com/viewjob?jk=8e4eaf7eaa027bbb</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full-stack Engineer 4 (Golang, Python, Java, AWS)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Data Lake, CI/CD, Git, Databricks, PySpark, Power BI, MicroStrategy, Python, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e85b5d56e27bdfb8</t>
+          <t>https://www.indeed.com/viewjob?jk=da278457dd975c3f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. iOS Developer--Hybrid</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Jenkins, Git, PostgreSQL, MySQL, Cassandra, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2f579d7993e4d2c</t>
+          <t>https://www.indeed.com/viewjob?jk=18716e78985d34c6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Full-stack Engineer 4 (Go, AWS)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c343a7d6432ffeaa</t>
+          <t>https://www.indeed.com/viewjob?jk=6132bb0eb6aaf86d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Full-stack Engineer 4 (GoLang)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e60054b9631d7895</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c24e0e87f3fc42</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Full-Stack Engineer 4 (Automation Quality Engineer)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Riverwoods, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99aade9079199e44</t>
+          <t>https://www.indeed.com/viewjob?jk=2acd23b24043f205</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Full-stack Engineer 4 - Shopping (Remote-Eligible)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb5a4840f3df3c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=f87b328e958cbb63</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Full-stack Engineer 5 (Golang, Python, GenAI) (Cloud Operations Resilience Engineering)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,67 +2281,67 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55abd889581cdc48</t>
+          <t>https://www.indeed.com/viewjob?jk=3c8f457b05bc7029</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Care Innovation - Senior Solution Architect 136-2001</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CommunityCare</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3febde783536e21</t>
+          <t>https://www.indeed.com/viewjob?jk=4f1669e27f9688a1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>R&amp;D Software Engineer (AI Developer Tooling), Intern</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>Generative AI, RAG, Prompt Engineering, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,19 +2351,19 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1be19f91eec7a842</t>
+          <t>https://www.indeed.com/viewjob?jk=cc131accf01fa9d0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2372,11 +2372,11 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>RAG, Synapse, CI/CD, Git, Snowflake, Databricks, PySpark, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7698c96689f48a9e</t>
+          <t>https://www.indeed.com/viewjob?jk=9724e994419d2473</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Data Scientist Associate</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>Data Scientist, RAG, Copilot, Git, Snowflake, Databricks, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2e1386f9d607f38</t>
+          <t>https://www.indeed.com/viewjob?jk=b87fe7f54c012f15</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Software Engineer III - AWS Data Platform Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>RAG, Glue, Athena, Redshift, CI/CD, Terraform, Redshift, Python, R, Java</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,67 +2456,67 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2ca862816ed069</t>
+          <t>https://www.indeed.com/viewjob?jk=db1a865cc7e5423a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Forward Deployed Engineer (Palantir Foundry &amp; Custom Development)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Jacobs</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>CI/CD, Git, Snowflake, Databricks, PostgreSQL, MongoDB, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a40909cafc968d82</t>
+          <t>https://www.indeed.com/viewjob?jk=e04a1c4764f16e30</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Machine Learning Engineer 4</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=124344ebd08b7526</t>
+          <t>https://www.indeed.com/viewjob?jk=21ed0ceedd301029</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Machine Learning Engineer 5 (IC)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0ef6c1eb38b0db9</t>
+          <t>https://www.indeed.com/viewjob?jk=ff0d8e13c3122e9c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Machine Learning Engineer 3</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b780dcc242beb567</t>
+          <t>https://www.indeed.com/viewjob?jk=c37251602c700f44</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Machine Learning Engineer 5 (IC)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a03180188c81f9bf</t>
+          <t>https://www.indeed.com/viewjob?jk=ad0c36d7f1a855e4</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Cloud Engineer 5</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a037168850b8fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=b93c76a2b8ee680e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Machine Learning Engineer 4</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45cd4b8d959d97ab</t>
+          <t>https://www.indeed.com/viewjob?jk=125927cd56c6a328</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Machine Learning Engineer 4</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52080037fabe4cb1</t>
+          <t>https://www.indeed.com/viewjob?jk=e3951c1b2b876911</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Machine Learning Engineer 4</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69224b4d176dd4a2</t>
+          <t>https://www.indeed.com/viewjob?jk=e91cbe985e056f4d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Machine Learning Engineer 5</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ce9dba6d19c8b82</t>
+          <t>https://www.indeed.com/viewjob?jk=e7d4aff57ff0fdfa</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Machine Learning Engineer 4</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,102 +2841,102 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c5344293aa5ed77</t>
+          <t>https://www.indeed.com/viewjob?jk=5055224391ab5f82</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Application Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ericsson</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fea3b3cc46faeb2a</t>
+          <t>https://www.indeed.com/viewjob?jk=0c841479d28f93ba</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>IT Analyst</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>RAG, Kinesis, Dataflow, Databricks, Kafka, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3672ad48951be20</t>
+          <t>https://www.indeed.com/viewjob?jk=84811fdfbe682535</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,172 +2946,172 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45dff0f36a9a356</t>
+          <t>https://www.indeed.com/viewjob?jk=0245dcafa3f48258</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Senior Systems Engineer - C/C++ Full Stack Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>SocioSquares</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>RAG, CI/CD, PostgreSQL, Python, SQL, R, C++, Scala, Optimization</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e91b7a712b7a165</t>
+          <t>https://www.indeed.com/viewjob?jk=0a718ffc683f8ff2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Care Innovation - Automation Engineer 136-2000</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CommunityCare</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>Generative AI, RAG, Prompt Engineering, CI/CD, GitHub Actions, Git, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d69f9412407b80</t>
+          <t>https://www.indeed.com/viewjob?jk=302eed7267c19c88</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Consultant, Software Engineer (Apigee, APIs, Kong)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, Python, R, Java</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d48fbbfaa3d0a97</t>
+          <t>https://www.indeed.com/viewjob?jk=1d33071a91f60b71</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Senior Software Engineer, Full Stack</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nexamp</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>RAG, FastAPI, CI/CD, Terraform, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c300f1e448116fd7</t>
+          <t>https://www.indeed.com/viewjob?jk=9b7f0e39754f677b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KeHE Distributors</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>AI Engineer, RAG, CI/CD, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=316adbd72ad7e2e8</t>
+          <t>https://www.indeed.com/viewjob?jk=9033c8036c6af9b3</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Full Stack Engineer 4, Enterprise CI/CD (AWS, Python, Groovy)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f219232c6b6eef2b</t>
+          <t>https://www.indeed.com/viewjob?jk=77931e54d32a9f5a</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Assoc Data Scientist</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Exelon</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Lombard, IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>Data Scientist, RAG, Hadoop, Dask, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bb31aa937d723cd</t>
+          <t>https://www.indeed.com/viewjob?jk=5c122a4acaae2096</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Machine Learning Intelligent Operations Team - Quant Analytics Senior Associate</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>RAG, XGBoost, LightGBM, Git, Snowflake, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,1197 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=884c614c785d6835</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ecedaabbce0a0b5b</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eea12c90a4a047af</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=28b6e9e7e6b5c6aa</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2c0e09d9843111bd</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3b10af7d10426fa4</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Full Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Kirby Building Systems</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Portland, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ba021890de8dea89</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Sr Forward Deployed Engineer (Palantir Foundry &amp; Custom Development)</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Jacobs</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Data Scientist, CI/CD, Git, Snowflake, Databricks, PostgreSQL, MongoDB, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=34498abb3a8be8a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Sr. Data Engineer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>WellSky</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Overland Park, KS, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, BigQuery, CI/CD, Git, BigQuery, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1d0888bf081a07cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Sally Beauty</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Denton, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>RAG, S3, Data Lake, Databricks, PySpark, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0864fe655aae7888</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Versant Health</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Troy, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Synapse, Data Lake, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=07b683fa1519b020</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Versant Health</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Synapse, Data Lake, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7a1725a49cda6dda</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Senior Consultant, AI Services</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>InvestorFlow</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Prompt Engineering, Git, Snowflake, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fba78e9af19a43b2</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Distributed Systems Engineer, Vehicle Fulfillment</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Tesla</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Fremont, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, LLaMA, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, R, Scala</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1a0fe96c02c778b6</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Senior Engineer -Creative Marketing</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Catalyst Brands</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, Git, Kafka, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b1a6e5202bbaaf18</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Sr Product Security Engineer, AI &amp; DevSecOps</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>McKesson</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b8ba8f92a1292eb</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Business Intelligence Engineer II: Partner Analytics - Hybrid</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Rocket</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Detroit, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, Snowflake, Tableau, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=637673cd1f7765b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Java Full Stack Developer-Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, Kafka, MongoDB, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0ee02388fd9a1d</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>SC Engineers</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Beltsville, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, Power BI, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2661c4a3a6b07f81</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Intentsify</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>S3, Docker, Kubernetes, AKS, CI/CD, Terraform, Snowflake, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6d89a533339b416c</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Software Engineer, ML Infrastructure, Level 5</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Snap Inc.</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4cad11433588f70d</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Sr Technical Analyst/Prog Ent App</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Avangrid</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Orange, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Generative AI, Copilot, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4ea1b275b8152311</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Mastercard</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Git, Snowflake, PostgreSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c33cfcad7d1aa65e</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Data Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Hubble Network</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Kinesis, Redshift, Kafka, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a000c1d1d33d8b12</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>AI engineer</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Writer</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc20f9386f214c0</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>AI engineer</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Writer</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3eb3f306bda536fb</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>AI Engineer I</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Universal Leaf Tobacco Company, Inc.</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Docker, Git, NoSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b8468e3514144cdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Data Science Intern - Summer 2027</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Rippling</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, AKS, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f2c869f55f6a0f6</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Community Choice Credit Union</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Warren, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>CI/CD, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=21899fbf482a9cd2</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Community Choice Credit Union</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Jackson, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>CI/CD, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9457f2c72938dbd5</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Community Choice Credit Union</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Holland, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>CI/CD, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6f79614628dc966f</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Community Choice Credit Union</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Farmington Hills, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>CI/CD, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4be70d8a478d8a</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Software engineer, agents</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Writer</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5700052fa2fc6f53</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Software engineer, agents</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Writer</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a8c6573ec630ba5a</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Software engineer, agents</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Writer</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cec61be25df497ab</t>
+          <t>https://www.indeed.com/viewjob?jk=50bcf2be164bc349</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-23.xlsx
+++ b/daily_matches/job_matches_2026-09-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,77 +468,77 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III - Generative AI Technology</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, TensorFlow, BigQuery, Data Lake, Dataflow, Kubernetes, CI/CD, GitHub Actions</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, BigQuery, MLflow, FastAPI, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dd495afc5140159</t>
+          <t>https://www.indeed.com/viewjob?jk=dea1b605e8c5ec18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Team TTI</t>
+          <t>United Utility</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Keras, MLflow, CI/CD, Databricks, Matplotlib</t>
+          <t>RAG, Redshift, BigQuery, Synapse, GitHub Actions, Git, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6df5f550c6a3e5b</t>
+          <t>https://www.indeed.com/viewjob?jk=2c848474306799be</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Data Engineer 4 (Python, AWS, Kafka, Spark, SQL, Snowflake, Databricks, GenAI)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -552,38 +552,38 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
+          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d80c6adab1193eaf</t>
+          <t>https://www.indeed.com/viewjob?jk=47e2de3bf66a6750</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer 5</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,24 +591,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
+          <t>Generative AI, RAG, Gemini, Prompt Engineering, CI/CD, GitHub Actions, Git, PostgreSQL, NoSQL, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a1e95e5123a2b15</t>
+          <t>https://www.indeed.com/viewjob?jk=1c826550112cce8f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer 5 - Enterprise Risk Management</t>
+          <t>Full Stack Engineer 4 (Python, AWS, AI, Snowflake, Databricks)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,59 +626,59 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Snowflake, Databricks, NoSQL, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a45f08af4f7be5f6</t>
+          <t>https://www.indeed.com/viewjob?jk=2d2e1578e6815ef7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer 4 - Nexus Products</t>
+          <t>Senior Software Engineer - Cloud Platform Engineering</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>MariaDB plc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
+          <t>LangChain, RAG, Docker, Kubernetes, CI/CD, Terraform, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36fc31dc37d05722</t>
+          <t>https://www.indeed.com/viewjob?jk=e683398c349f7a6d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Full-Stack Engineer 4 (Java, Spring, DynamoDB, S3, GraphQL, GenAI)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,32 +688,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
+          <t>RAG, Copilot, S3, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e14228c1ed2aed</t>
+          <t>https://www.indeed.com/viewjob?jk=30dd4b0534b4aca9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer 4 - Payment Networks</t>
+          <t>Full-Stack Engineer 4 (Java, Spring, DynamoDB, S3, GraphQL, GenAL)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -727,243 +727,243 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
+          <t>RAG, Copilot, S3, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8d0c3f139798fd9</t>
+          <t>https://www.indeed.com/viewjob?jk=3e502713d51d0a40</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer 4 - HR Tech</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=010f3637940ea854</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e88687923bfcde</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer 5 (SEO/GEO, AdTech )</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9a8f6941c1a4549</t>
+          <t>https://www.indeed.com/viewjob?jk=23ca0cd83e1c704c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0db4720c664a5a3f</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5e690d9659ab0e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer 5 (Enterprise Platforms Technology)</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Florence, AL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=220dab7fe793042b</t>
+          <t>https://www.indeed.com/viewjob?jk=478d3913715a36d5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - Operations</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Manassas, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Keras, MLflow, CI/CD, Databricks, Matplotlib</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1f1b289a3e5556a</t>
+          <t>https://www.indeed.com/viewjob?jk=5ae07b7c08a9ee08</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Go, TypeScript and Angular)</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>La Crosse, WI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81ff3ef325447a98</t>
+          <t>https://www.indeed.com/viewjob?jk=aa5347b5729959fc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Nodejs/Go/Angularjs)</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -972,1341 +972,1341 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9813442a220867be</t>
+          <t>https://www.indeed.com/viewjob?jk=b2771dea7e7bebc0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70843ae9e366dd5b</t>
+          <t>https://www.indeed.com/viewjob?jk=e978e398ad967da0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Full - Stack Engineer 5 (Remote - Eligible)</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Elk Grove, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877ad6c20024fb1a</t>
+          <t>https://www.indeed.com/viewjob?jk=dfb27bc9bc8fc3fd</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6979868bb95d63f0</t>
+          <t>https://www.indeed.com/viewjob?jk=7bf26a5704e50db1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 - RiskTech</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2960b2498873f28</t>
+          <t>https://www.indeed.com/viewjob?jk=3d05cc5a9f520e98</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 5</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b743b91aec079a75</t>
+          <t>https://www.indeed.com/viewjob?jk=ac7aefa56e3dd9a8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb66ff5f4ef065f</t>
+          <t>https://www.indeed.com/viewjob?jk=b195226ebcad916e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Python, Java)</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Franklin, TN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9046de91e154d69</t>
+          <t>https://www.indeed.com/viewjob?jk=2586760df9fb98ff</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 ( Python, AWS)</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e4de127a7227d81</t>
+          <t>https://www.indeed.com/viewjob?jk=7aebc535d5559f35</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Golang, Java, AWS)</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3a9ee8f682a9c78</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c8653fa3538db6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6faf5ca1640fcd31</t>
+          <t>https://www.indeed.com/viewjob?jk=5c8aa777d4875c5c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42133a298638cb9b</t>
+          <t>https://www.indeed.com/viewjob?jk=5708c8b21a8b26c0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a708182f9a1da64d</t>
+          <t>https://www.indeed.com/viewjob?jk=43de1e64a22d9cd2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Issaquah, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76c8a5b4fcc58505</t>
+          <t>https://www.indeed.com/viewjob?jk=f032eff8cdf1f51c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 - Shopping (Remote-Eligible)</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=419688dc0cbfaf98</t>
+          <t>https://www.indeed.com/viewjob?jk=106d69456e114d56</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Java, Scala, AWS)</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Greeley, CO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c997daa05db4e0c7</t>
+          <t>https://www.indeed.com/viewjob?jk=38cc6912fc4fff9a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4 (Go, AWS)</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a9874c783fb4a03</t>
+          <t>https://www.indeed.com/viewjob?jk=1ea8ed0ca16d81ca</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Buffalo Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f96da918db85a2a</t>
+          <t>https://www.indeed.com/viewjob?jk=192930961104758a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Java, Scala, AWS)</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9e0187cbe4c2e40</t>
+          <t>https://www.indeed.com/viewjob?jk=55a54c8e78be5249</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=900df92ddc778d5f</t>
+          <t>https://www.indeed.com/viewjob?jk=2e7ccf71af0d4da5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (JavaScript, React)</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Gainesville, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7c346fa6453ffb9</t>
+          <t>https://www.indeed.com/viewjob?jk=c0551318b5b522ef</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Go/Java, Angular, AWS)</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c039bc465260bc95</t>
+          <t>https://www.indeed.com/viewjob?jk=eef38f176c0e4573</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Jefferson, WI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e236865193f8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=c5e04e5085d0f3f6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b667ebd325202576</t>
+          <t>https://www.indeed.com/viewjob?jk=4626717641b97a9c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Golang, AWS)</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672e371e8fd60859</t>
+          <t>https://www.indeed.com/viewjob?jk=7ba338fc39f9e484</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (React, TypeScript, AWS)</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Lewes, DE, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346a7f081a67b46c</t>
+          <t>https://www.indeed.com/viewjob?jk=27ab5cfe17121b8c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Coppell, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b21934bf2433e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=ac3361eea54e00bb</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Scala, React, AWS)</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hilo, HI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2af3b2e528eb8c47</t>
+          <t>https://www.indeed.com/viewjob?jk=22fa515a90f7160f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Scala, React, AWS)</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51fd20841ca9c754</t>
+          <t>https://www.indeed.com/viewjob?jk=eec3c59827b0acff</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Franklin, TN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619531dae358928f</t>
+          <t>https://www.indeed.com/viewjob?jk=e9a140d34aa32532</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Python, AWS)</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Fort Collins, CO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e4eaf7eaa027bbb</t>
+          <t>https://www.indeed.com/viewjob?jk=e88e0e6d93102b1a</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Golang, Python, Java, AWS)</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da278457dd975c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=93ff95ea45b04385</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18716e78985d34c6</t>
+          <t>https://www.indeed.com/viewjob?jk=5c188011cdba12b6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Go, AWS)</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6132bb0eb6aaf86d</t>
+          <t>https://www.indeed.com/viewjob?jk=640c531fa6e2f2b4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (GoLang)</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c24e0e87f3fc42</t>
+          <t>https://www.indeed.com/viewjob?jk=7dbc623ad523c949</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Automation Quality Engineer)</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Riverwoods, IL, US USA</t>
+          <t>Buffalo Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2acd23b24043f205</t>
+          <t>https://www.indeed.com/viewjob?jk=c2cb4c0c01eb8a51</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 - Shopping (Remote-Eligible)</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Leominster, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f87b328e958cbb63</t>
+          <t>https://www.indeed.com/viewjob?jk=d93bf3129b8f1f40</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Golang, Python, GenAI) (Cloud Operations Resilience Engineering)</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c8f457b05bc7029</t>
+          <t>https://www.indeed.com/viewjob?jk=ce5a6640c3e3a615</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Care Innovation - Senior Solution Architect 136-2001</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CommunityCare</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,172 +2316,172 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f1669e27f9688a1</t>
+          <t>https://www.indeed.com/viewjob?jk=d2a355e53b5aee04</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>R&amp;D Software Engineer (AI Developer Tooling), Intern</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc131accf01fa9d0</t>
+          <t>https://www.indeed.com/viewjob?jk=a843d240e47bb50d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RAG, Synapse, CI/CD, Git, Snowflake, Databricks, PySpark, Power BI, Python, SQL</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9724e994419d2473</t>
+          <t>https://www.indeed.com/viewjob?jk=802de18a676e0b71</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Scientist Associate</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Git, Snowflake, Databricks, Tableau, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b87fe7f54c012f15</t>
+          <t>https://www.indeed.com/viewjob?jk=c90c9293c67e26e2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS Data Platform Engineer</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Cody, WY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RAG, Glue, Athena, Redshift, CI/CD, Terraform, Redshift, Python, R, Java</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db1a865cc7e5423a</t>
+          <t>https://www.indeed.com/viewjob?jk=dea3ed9657eb8d2d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (Palantir Foundry &amp; Custom Development)</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Jacobs</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CI/CD, Git, Snowflake, Databricks, PostgreSQL, MongoDB, Python, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,417 +2491,417 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e04a1c4764f16e30</t>
+          <t>https://www.indeed.com/viewjob?jk=fad997d5c6b37de5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 4</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21ed0ceedd301029</t>
+          <t>https://www.indeed.com/viewjob?jk=5eecdbb637840111</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 5 (IC)</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff0d8e13c3122e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c6f58239a9a7f9</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 3</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Columbus, MS, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37251602c700f44</t>
+          <t>https://www.indeed.com/viewjob?jk=afded3ea6ad0f2d6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 5 (IC)</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad0c36d7f1a855e4</t>
+          <t>https://www.indeed.com/viewjob?jk=45ab5afc31123292</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cloud Engineer 5</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>La Quinta, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b93c76a2b8ee680e</t>
+          <t>https://www.indeed.com/viewjob?jk=560b4890bef57ed3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 4</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=125927cd56c6a328</t>
+          <t>https://www.indeed.com/viewjob?jk=ecc7c71438c05804</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 4</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3951c1b2b876911</t>
+          <t>https://www.indeed.com/viewjob?jk=1d0e206f81866fd5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 4</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Carbondale, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e91cbe985e056f4d</t>
+          <t>https://www.indeed.com/viewjob?jk=eaaff0d077502734</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 5</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7d4aff57ff0fdfa</t>
+          <t>https://www.indeed.com/viewjob?jk=73c319dbadf52415</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 4</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5055224391ab5f82</t>
+          <t>https://www.indeed.com/viewjob?jk=bff2cc411884dd58</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Application Engineer</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ericsson</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c841479d28f93ba</t>
+          <t>https://www.indeed.com/viewjob?jk=d2c371c533aa9ccf</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>IT Analyst</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RAG, Kinesis, Dataflow, Databricks, Kafka, Power BI, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,67 +2911,67 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84811fdfbe682535</t>
+          <t>https://www.indeed.com/viewjob?jk=7a9bf786f0eaa98a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Carrollton, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0245dcafa3f48258</t>
+          <t>https://www.indeed.com/viewjob?jk=fa7060b3253326ee</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer - C/C++ Full Stack Developer</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SocioSquares</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, PostgreSQL, Python, SQL, R, C++, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a718ffc683f8ff2</t>
+          <t>https://www.indeed.com/viewjob?jk=174cb30f33f222dd</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Care Innovation - Automation Engineer 136-2000</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CommunityCare</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, CI/CD, GitHub Actions, Git, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=302eed7267c19c88</t>
+          <t>https://www.indeed.com/viewjob?jk=17b34127e4e373f6</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Consultant, Software Engineer (Apigee, APIs, Kong)</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, Python, R, Java</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d33071a91f60b71</t>
+          <t>https://www.indeed.com/viewjob?jk=52076093ad6dfc7c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full Stack</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Nexamp</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, CI/CD, Terraform, Git, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,147 +3086,1022 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7f0e39754f677b</t>
+          <t>https://www.indeed.com/viewjob?jk=c54cd124dfca846d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>KeHE Distributors</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, CI/CD, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9033c8036c6af9b3</t>
+          <t>https://www.indeed.com/viewjob?jk=893413cf4629d8e0</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4, Enterprise CI/CD (AWS, Python, Groovy)</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77931e54d32a9f5a</t>
+          <t>https://www.indeed.com/viewjob?jk=2ed8251869808e55</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Assoc Data Scientist</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Exelon</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Lombard, IL, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Hadoop, Dask, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c122a4acaae2096</t>
+          <t>https://www.indeed.com/viewjob?jk=658edc4064441a8f</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Machine Learning Intelligent Operations Team - Quant Analytics Senior Associate</t>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de4661931c0551fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Hudson Manpower</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d73a5d61a96572f</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Hudson Manpower</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>San Francisco Bay Area, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7dbd5536ad64ce09</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Hudson Manpower</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3128973e16183783</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Hudson Manpower</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Beachwood, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=907323bc9279012a</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Hudson Manpower</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f3f64d69483218f</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Hudson Manpower</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Bloomington, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09726b911d3017a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Hudson Manpower</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7a7ff8f68153967c</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Generative AI/ML - Full Time Role - USC and GC's only</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Hudson Manpower</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aae315c07444ddca</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4 (IC)</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4620494dca257198</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4 (IC)</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6b1bed8feba6b917</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e194fdfb9b8dbe3</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Full-Stack Engineer 4 (Python, AWS, Network Automation)</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a77780c738e44a57</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Machine Learning Scientist III, Ads Optimization &amp; Automation</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Wayfair</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, BigQuery, MLflow, BigQuery, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c413dffa7ee3f96b</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Scientist - Recommendations</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Wayfair</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, MLflow, Hadoop, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b27dc18cb51c8654</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Machine Learning Scientist I</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Wayfair</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Docker, CI/CD, Git, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5500d998f5b43e33</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>AI Agent Developer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Strues Inc</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Glue, Athena, Redshift, Redshift, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c887ae1e11a45de2</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer 5 (IC)</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc5dc747c592d8e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Data Scientist IV</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>CareSource</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, CI/CD, Snowflake, Databricks, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f79ced955268a69b</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Machine Learning Science Intern - Summer 2027</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Wayfair</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>RAG, PyTorch, Docker, Git, PySpark, Python, SQL, R, Scala, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5bb5ee4c0563f4fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Sr. Ecommerce Analyst</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Box</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
         <v>10</v>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>RAG, XGBoost, LightGBM, Git, Snowflake, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=50bcf2be164bc349</t>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Git, Snowflake, BigQuery, Tableau, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c0b58f1cdd0bba8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Software Data Engineer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Burbank, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Data Scientist, Terraform, Git, Snowflake, Databricks, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7c87c0c0d2d3ec3</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Hasbro, Inc.</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Renton, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Kafka, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a4789698147fb9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Hasbro, Inc.</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Renton, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Kafka, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=431b277a53c2487f</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Machine Learning Scientist III - Ads + Search &amp; Recommendations</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Wayfair</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, MLflow, Docker, BigQuery, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=23a15fdcf3515689</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Machine Learning Scientist II - Pricing &amp; Economics</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Wayfair</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>RAG, XGBoost, MLflow, Docker, Kubernetes, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3e1ff77eb389b355</t>
         </is>
       </c>
     </row>
